--- a/top10_by_country_inflection.xlsx
+++ b/top10_by_country_inflection.xlsx
@@ -708,26 +708,26 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>LONG.BA</t>
+          <t>BYMA.BA</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>Longvie S.A.</t>
+          <t>Bolsas y Mercados Argentinos S.A.</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H5" s="11" t="n">
-        <v>9707070464</v>
+        <v>2294352445440</v>
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
@@ -735,16 +735,16 @@
         </is>
       </c>
       <c r="J5" s="13" t="n">
-        <v>0.3913422366405466</v>
+        <v>0.3771931277056725</v>
       </c>
       <c r="K5" s="13" t="n">
-        <v>0.3506586413338435</v>
+        <v>0.3774551911094</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>0.45</v>
+        <v>0.322729</v>
       </c>
       <c r="M5" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -763,26 +763,26 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>VALO.BA</t>
+          <t>LONG.BA</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Grupo Financiero Valores S.A.</t>
+          <t>Longvie S.A.</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H6" s="11" t="n">
-        <v>775063666688</v>
+        <v>9707070464</v>
       </c>
       <c r="I6" s="15" t="inlineStr">
         <is>
@@ -790,16 +790,16 @@
         </is>
       </c>
       <c r="J6" s="13" t="n">
-        <v>0.3056257434994442</v>
+        <v>0.3913422366405466</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>0.4152547471956278</v>
+        <v>0.3506586413338435</v>
       </c>
       <c r="L6" s="13" t="n">
-        <v>0.5869220000000001</v>
+        <v>0.45</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -818,17 +818,17 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>CECO2.BA</t>
+          <t>VALO.BA</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Enel Generacion Costanera S.A.</t>
+          <t>Grupo Financiero Valores S.A.</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
@@ -837,24 +837,24 @@
         </is>
       </c>
       <c r="H7" s="11" t="n">
-        <v>346782236672</v>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>775063666688</v>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J7" s="13" t="n">
-        <v>0.3203783755699272</v>
+        <v>0.3056257434994442</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>0.4095969232373488</v>
+        <v>0.4152547471956278</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>0.741105</v>
+        <v>0.5869220000000001</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -873,43 +873,43 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>BYMA.BA</t>
+          <t>CECO2.BA</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Bolsas y Mercados Argentinos S.A.</t>
+          <t>Enel Generacion Costanera S.A.</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H8" s="11" t="n">
-        <v>2294352445440</v>
-      </c>
-      <c r="I8" s="15" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>346782236672</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="J8" s="13" t="n">
-        <v>0.312752019525081</v>
+        <v>0.3203783755699272</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>0.3129693110204428</v>
+        <v>0.4095969232373488</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>0.322729</v>
+        <v>0.741105</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="J14" s="13" t="n">
-        <v>0.4725691393511089</v>
+        <v>0.5732919298430178</v>
       </c>
       <c r="K14" s="13" t="n">
-        <v>0.3375004952202665</v>
+        <v>0.4094349252121699</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>0.313824</v>
+        <v>0.391612</v>
       </c>
       <c r="M14" s="11" t="n">
         <v>3</v>
@@ -1285,13 +1285,13 @@
         </is>
       </c>
       <c r="J15" s="13" t="n">
-        <v>0.4679569477074025</v>
+        <v>0.5327871324524621</v>
       </c>
       <c r="K15" s="13" t="n">
-        <v>0.3986716631732392</v>
+        <v>0.4539031491096375</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>0.510705</v>
+        <v>0.559733</v>
       </c>
       <c r="M15" s="11" t="n">
         <v>1</v>
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="J19" s="13" t="n">
-        <v>0.3447037130220343</v>
+        <v>0.3424204577934261</v>
       </c>
       <c r="K19" s="13" t="n">
-        <v>0.3145135298803299</v>
+        <v>0.3124302489801286</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>0.34871</v>
+        <v>0.335649</v>
       </c>
       <c r="M19" s="11" t="n">
         <v>0</v>
@@ -1560,13 +1560,13 @@
         </is>
       </c>
       <c r="J20" s="13" t="n">
-        <v>0.4052232684918046</v>
+        <v>0.3956002470055242</v>
       </c>
       <c r="K20" s="13" t="n">
-        <v>0.4433745152714897</v>
+        <v>0.4328454987547271</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>0.675305</v>
+        <v>0.578192</v>
       </c>
       <c r="M20" s="11" t="n">
         <v>3</v>
@@ -1780,13 +1780,13 @@
         </is>
       </c>
       <c r="J24" s="13" t="n">
-        <v>0.5844787751742412</v>
+        <v>0.5888251966660882</v>
       </c>
       <c r="K24" s="13" t="n">
-        <v>0.4472755132093951</v>
+        <v>0.4506016355357546</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>0.332367</v>
+        <v>0.354426</v>
       </c>
       <c r="M24" s="11" t="n">
         <v>3</v>
@@ -2028,43 +2028,43 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>INV.AX</t>
+          <t>LSX.AX</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>InvestSMART Group Limited</t>
+          <t>Lion Selection Group Limited</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H29" s="11" t="n">
-        <v>19188784</v>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>121759088</v>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J29" s="13" t="n">
-        <v>0.4418308935443055</v>
+        <v>0.4480176397471303</v>
       </c>
       <c r="K29" s="13" t="n">
-        <v>0.4676329833637714</v>
+        <v>0.4813351315413793</v>
       </c>
       <c r="L29" s="13" t="n">
-        <v>0.383117</v>
+        <v>0.550889</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2083,40 +2083,40 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>BRK.AX</t>
+          <t>INV.AX</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>Brookside Energy Limited</t>
+          <t>InvestSMART Group Limited</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H30" s="11" t="n">
-        <v>44327860</v>
-      </c>
-      <c r="I30" s="12" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>19188784</v>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="J30" s="13" t="n">
-        <v>0.501366546554772</v>
+        <v>0.4370752545238183</v>
       </c>
       <c r="K30" s="13" t="n">
-        <v>0.4843885758482467</v>
+        <v>0.4625996240051447</v>
       </c>
       <c r="L30" s="13" t="n">
-        <v>0.405213</v>
+        <v>0.350826</v>
       </c>
       <c r="M30" s="11" t="n">
         <v>3</v>
@@ -2138,17 +2138,17 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>CLV.AX</t>
+          <t>BRK.AX</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>Clover Corporation Limited</t>
+          <t>Brookside Energy Limited</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="H31" s="11" t="n">
-        <v>149464416</v>
+        <v>44327860</v>
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
@@ -2165,16 +2165,16 @@
         </is>
       </c>
       <c r="J31" s="13" t="n">
-        <v>0.3088749327435483</v>
+        <v>0.501366546554772</v>
       </c>
       <c r="K31" s="13" t="n">
-        <v>0.4611305383455422</v>
+        <v>0.4843885758482467</v>
       </c>
       <c r="L31" s="13" t="n">
-        <v>0.566427</v>
+        <v>0.405213</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2193,26 +2193,26 @@
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>GRR.AX</t>
+          <t>SUN.AX</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>Grange Resources Ltd.</t>
+          <t>Suncorp Group Limited</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="H32" s="11" t="n">
-        <v>190960896</v>
+        <v>18724509696</v>
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
@@ -2220,16 +2220,16 @@
         </is>
       </c>
       <c r="J32" s="13" t="n">
-        <v>0.5833492453719451</v>
+        <v>0.4939354726122924</v>
       </c>
       <c r="K32" s="13" t="n">
-        <v>0.4121050366023343</v>
+        <v>0.4519555696747713</v>
       </c>
       <c r="L32" s="13" t="n">
-        <v>0.517012</v>
+        <v>0.627736</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -2248,17 +2248,17 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>FWD.AX</t>
+          <t>MCA.AX</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>Fleetwood Limited</t>
+          <t>Murray Cod Australia Limited</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="H33" s="11" t="n">
-        <v>157850768</v>
+        <v>25237732</v>
       </c>
       <c r="I33" s="15" t="inlineStr">
         <is>
@@ -2275,16 +2275,16 @@
         </is>
       </c>
       <c r="J33" s="13" t="n">
-        <v>0.4915846785563</v>
+        <v>0.5100775989052906</v>
       </c>
       <c r="K33" s="13" t="n">
-        <v>0.4635354199538016</v>
+        <v>0.4568473086443722</v>
       </c>
       <c r="L33" s="13" t="n">
-        <v>0.976504</v>
+        <v>0.626341</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -2523,26 +2523,26 @@
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>SPA.BR</t>
+          <t>AGS.BR</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Societe de Services, de Participations, de Direction et d'El</t>
+          <t>ageas SA/NV</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="H38" s="11" t="n">
-        <v>1477524608</v>
+        <v>14363478016</v>
       </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
@@ -2550,13 +2550,13 @@
         </is>
       </c>
       <c r="J38" s="13" t="n">
-        <v>0.2496412586639294</v>
+        <v>0.3965022673093251</v>
       </c>
       <c r="K38" s="13" t="n">
-        <v>0.3837974176954301</v>
+        <v>0.3013153051633526</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>0.425585</v>
+        <v>0.544967</v>
       </c>
       <c r="M38" s="11" t="n">
         <v>1</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>UMI.BR</t>
+          <t>MOUR.BR</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Umicore SA</t>
+          <t>Moury Construct SA</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
@@ -2593,11 +2593,11 @@
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H39" s="11" t="n">
-        <v>6264232448</v>
+        <v>308123392</v>
       </c>
       <c r="I39" s="15" t="inlineStr">
         <is>
@@ -2605,16 +2605,16 @@
         </is>
       </c>
       <c r="J39" s="13" t="n">
-        <v>0.1596511203393669</v>
+        <v>0.3248046552737748</v>
       </c>
       <c r="K39" s="13" t="n">
-        <v>0.3433142219588678</v>
+        <v>0.4283804197705759</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>0.449949</v>
+        <v>0.696888</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>MIKO.BR</t>
+          <t>SPA.BR</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>Miko NV</t>
+          <t>Societe de Services, de Participations, de Direction et d'El</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
@@ -2648,11 +2648,11 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H40" s="11" t="n">
-        <v>72036000</v>
+        <v>1477524608</v>
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
@@ -2660,13 +2660,13 @@
         </is>
       </c>
       <c r="J40" s="13" t="n">
-        <v>0.3403879647690271</v>
+        <v>0.2496412586639294</v>
       </c>
       <c r="K40" s="13" t="n">
-        <v>0.405976915615002</v>
+        <v>0.3837974176954301</v>
       </c>
       <c r="L40" s="13" t="n">
-        <v>0.737615</v>
+        <v>0.425585</v>
       </c>
       <c r="M40" s="11" t="n">
         <v>1</v>
@@ -2688,12 +2688,12 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>JEN.BR</t>
+          <t>UMI.BR</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>Jensen-Group NV</t>
+          <t>Umicore SA</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
@@ -2703,11 +2703,11 @@
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="H41" s="11" t="n">
-        <v>701007808</v>
+        <v>6264232448</v>
       </c>
       <c r="I41" s="15" t="inlineStr">
         <is>
@@ -2715,16 +2715,16 @@
         </is>
       </c>
       <c r="J41" s="13" t="n">
-        <v>0.2869790287900399</v>
+        <v>0.1596511203393669</v>
       </c>
       <c r="K41" s="13" t="n">
-        <v>0.3676925796063129</v>
+        <v>0.3433142219588678</v>
       </c>
       <c r="L41" s="13" t="n">
-        <v>0.629788</v>
+        <v>0.449949</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -2743,17 +2743,17 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>MOUR.BR</t>
+          <t>MIKO.BR</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>Moury Construct SA</t>
+          <t>Miko NV</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="H42" s="11" t="n">
-        <v>308123392</v>
+        <v>72036000</v>
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
@@ -2770,16 +2770,16 @@
         </is>
       </c>
       <c r="J42" s="13" t="n">
-        <v>0.2693137929259604</v>
+        <v>0.3403879647690271</v>
       </c>
       <c r="K42" s="13" t="n">
-        <v>0.3551942799784861</v>
+        <v>0.405976915615002</v>
       </c>
       <c r="L42" s="13" t="n">
-        <v>0.696888</v>
+        <v>0.737615</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2798,26 +2798,26 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>BAR.BR</t>
+          <t>JEN.BR</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>Barco NV</t>
+          <t>Jensen-Group NV</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H43" s="11" t="n">
-        <v>745517120</v>
+        <v>701007808</v>
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
@@ -2825,16 +2825,16 @@
         </is>
       </c>
       <c r="J43" s="13" t="n">
-        <v>0.4073839192631131</v>
+        <v>0.2869790287900399</v>
       </c>
       <c r="K43" s="13" t="n">
-        <v>0.4366433380735786</v>
+        <v>0.3676925796063129</v>
       </c>
       <c r="L43" s="13" t="n">
-        <v>0.85588</v>
+        <v>0.629788</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2990,13 +2990,13 @@
         </is>
       </c>
       <c r="J46" s="13" t="n">
-        <v>0.555729837694053</v>
+        <v>0.5507670961041651</v>
       </c>
       <c r="K46" s="13" t="n">
-        <v>0.4843279603345583</v>
+        <v>0.4800028470351332</v>
       </c>
       <c r="L46" s="13" t="n">
-        <v>0.82196</v>
+        <v>0.787203</v>
       </c>
       <c r="M46" s="11" t="n">
         <v>3</v>
@@ -3045,13 +3045,13 @@
         </is>
       </c>
       <c r="J47" s="13" t="n">
-        <v>0.4185742929765297</v>
+        <v>0.4169728901907558</v>
       </c>
       <c r="K47" s="13" t="n">
-        <v>0.4457923395721812</v>
+        <v>0.4440868046015766</v>
       </c>
       <c r="L47" s="13" t="n">
-        <v>0.71553</v>
+        <v>0.699554</v>
       </c>
       <c r="M47" s="11" t="n">
         <v>3</v>
@@ -3183,26 +3183,26 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>DOHL3.SA</t>
+          <t>IRBR3.SA</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>Dohler S.A.</t>
+          <t>IRB-Brasil Resseguros S.A.</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H50" s="11" t="n">
-        <v>489565664</v>
+        <v>4279219200</v>
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
@@ -3210,16 +3210,16 @@
         </is>
       </c>
       <c r="J50" s="13" t="n">
-        <v>0.4385426933592537</v>
+        <v>0.5693286568729902</v>
       </c>
       <c r="K50" s="13" t="n">
-        <v>0.4118663916095332</v>
+        <v>0.4559465926974371</v>
       </c>
       <c r="L50" s="13" t="n">
-        <v>0.635157</v>
+        <v>0.538142</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3238,17 +3238,17 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>MTSA4.SA</t>
+          <t>DOHL3.SA</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>METISA Metalurgica Timboense S.A.</t>
+          <t>Dohler S.A.</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
@@ -3257,24 +3257,24 @@
         </is>
       </c>
       <c r="H51" s="11" t="n">
-        <v>400949728</v>
-      </c>
-      <c r="I51" s="16" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>489565664</v>
+      </c>
+      <c r="I51" s="15" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J51" s="13" t="n">
-        <v>0.4625812642268837</v>
+        <v>0.4385426933592537</v>
       </c>
       <c r="K51" s="13" t="n">
-        <v>0.5145850218006855</v>
+        <v>0.4118663916095332</v>
       </c>
       <c r="L51" s="13" t="n">
-        <v>0.870427</v>
+        <v>0.635157</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>AZEV3.SA</t>
+          <t>MTSA4.SA</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Azevedo &amp; Travassos S.A.</t>
+          <t>METISA Metalurgica Timboense S.A.</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
@@ -3308,28 +3308,28 @@
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H52" s="11" t="n">
-        <v>106696008</v>
-      </c>
-      <c r="I52" s="15" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>400949728</v>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="J52" s="13" t="n">
-        <v>0.3407997985546886</v>
+        <v>0.4625812642268837</v>
       </c>
       <c r="K52" s="13" t="n">
-        <v>0.374264990109608</v>
+        <v>0.5145850218006855</v>
       </c>
       <c r="L52" s="13" t="n">
-        <v>0.398468</v>
+        <v>0.870427</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3348,26 +3348,26 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>USIM5.SA</t>
+          <t>AZEV3.SA</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Usinas Siderurgicas de Minas Gerais S.A.</t>
+          <t>Azevedo &amp; Travassos S.A.</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H53" s="11" t="n">
-        <v>12592543744</v>
+        <v>106696008</v>
       </c>
       <c r="I53" s="15" t="inlineStr">
         <is>
@@ -3375,16 +3375,16 @@
         </is>
       </c>
       <c r="J53" s="13" t="n">
-        <v>0.3206084907939679</v>
+        <v>0.3407997985546886</v>
       </c>
       <c r="K53" s="13" t="n">
-        <v>0.388648107134924</v>
+        <v>0.374264990109608</v>
       </c>
       <c r="L53" s="13" t="n">
-        <v>0.502757</v>
+        <v>0.398468</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -13688,12 +13688,12 @@
       </c>
       <c r="D241" s="8" t="inlineStr">
         <is>
-          <t>VIS.IC</t>
+          <t>ARION.IC</t>
         </is>
       </c>
       <c r="E241" s="9" t="inlineStr">
         <is>
-          <t>Vatryggingafelag √çslands hf.</t>
+          <t>Arion banki hf.</t>
         </is>
       </c>
       <c r="F241" s="10" t="inlineStr">
@@ -13703,11 +13703,11 @@
       </c>
       <c r="G241" s="10" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mega Cap</t>
         </is>
       </c>
       <c r="H241" s="11" t="n">
-        <v>29853863936</v>
+        <v>264194211840</v>
       </c>
       <c r="I241" s="15" t="inlineStr">
         <is>
@@ -13721,10 +13721,10 @@
         <v>0</v>
       </c>
       <c r="L241" s="13" t="n">
-        <v>0.474975</v>
+        <v>0.580385</v>
       </c>
       <c r="M241" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -13743,12 +13743,12 @@
       </c>
       <c r="D242" s="8" t="inlineStr">
         <is>
-          <t>ARION.IC</t>
+          <t>KVIKA.IC</t>
         </is>
       </c>
       <c r="E242" s="9" t="inlineStr">
         <is>
-          <t>Arion banki hf.</t>
+          <t>Kvika banki hf.</t>
         </is>
       </c>
       <c r="F242" s="10" t="inlineStr">
@@ -13758,11 +13758,11 @@
       </c>
       <c r="G242" s="10" t="inlineStr">
         <is>
-          <t>Mega Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="H242" s="11" t="n">
-        <v>264194211840</v>
+        <v>73290391552</v>
       </c>
       <c r="I242" s="15" t="inlineStr">
         <is>
@@ -13776,10 +13776,10 @@
         <v>0</v>
       </c>
       <c r="L242" s="13" t="n">
-        <v>0.580385</v>
+        <v>0.253374</v>
       </c>
       <c r="M242" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
@@ -13798,12 +13798,12 @@
       </c>
       <c r="D243" s="8" t="inlineStr">
         <is>
-          <t>KVIKA.IC</t>
+          <t>VIS.IC</t>
         </is>
       </c>
       <c r="E243" s="9" t="inlineStr">
         <is>
-          <t>Kvika banki hf.</t>
+          <t>Vatryggingafelag √çslands hf.</t>
         </is>
       </c>
       <c r="F243" s="10" t="inlineStr">
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="H243" s="11" t="n">
-        <v>73290391552</v>
+        <v>29853863936</v>
       </c>
       <c r="I243" s="15" t="inlineStr">
         <is>
@@ -13831,10 +13831,10 @@
         <v>0</v>
       </c>
       <c r="L243" s="13" t="n">
-        <v>0.253374</v>
+        <v>0.474975</v>
       </c>
       <c r="M243" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">

--- a/top10_by_country_inflection.xlsx
+++ b/top10_by_country_inflection.xlsx
@@ -29,33 +29,33 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <b val="1"/>
       <color rgb="00404040"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <color rgb="00707070"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <i val="1"/>
       <color rgb="00707070"/>
       <sz val="10"/>
